--- a/originales/respuestas/2025/01. Calificadas/bucle p35/Agencia Distrital Para La Educación Superior, La Ciencia Y La Tecnología.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p35/Agencia Distrital Para La Educación Superior, La Ciencia Y La Tecnología.xlsx
@@ -221,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -236,9 +236,6 @@
     </xf>
     <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -530,31 +527,31 @@
       <c r="F2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="4">
         <v>3.0</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="4">
         <v>3.0</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="4">
         <v>3.0</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="4">
         <v>3.0</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="4">
         <v>4.0</v>
       </c>
       <c r="P2" s="4"/>
@@ -578,31 +575,31 @@
       <c r="F3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="4">
         <v>5.0</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="4">
         <v>5.0</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="4">
         <v>5.0</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="4">
         <v>5.0</v>
       </c>
       <c r="N3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="5">
+      <c r="O3" s="4">
         <v>5.0</v>
       </c>
       <c r="P3" s="4"/>
@@ -626,31 +623,31 @@
       <c r="F4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>4.0</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="4">
         <v>5.0</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="4">
         <v>5.0</v>
       </c>
       <c r="L4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="4">
         <v>5.0</v>
       </c>
       <c r="N4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="5">
+      <c r="O4" s="4">
         <v>5.0</v>
       </c>
       <c r="P4" s="4"/>
